--- a/Result/Ranking_Overall.xlsx
+++ b/Result/Ranking_Overall.xlsx
@@ -664,204 +664,219 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>MDO</t>
+          <t>MC-RBO</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>0.8277035659171585</v>
+        <v>0.8327105130156982</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.7467427235483085</v>
+        <v>0.7428242427788448</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.9232510855010778</v>
+        <v>0.9213687155427421</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.7825002527775332</v>
+        <v>0.7810295547576495</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.3370141090088984</v>
+        <v>55.060859978523</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>NROMM</t>
+          <t>MDO</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>0.834154222350256</v>
+        <v>0.8277035659171585</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.7605219134493326</v>
+        <v>0.7467427235483085</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.9225946532138157</v>
+        <v>0.9232510855010778</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.776679911796895</v>
+        <v>0.7825002527775332</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>62.3870712900904</v>
+        <v>0.3370141090088984</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>OREM-M</t>
+          <t>NROMM</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>0.8372971000464409</v>
+        <v>0.834154222350256</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.7757433716610412</v>
+        <v>0.7605219134493326</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.9236600338426921</v>
+        <v>0.9225946532138157</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.7731972949465373</v>
+        <v>0.776679911796895</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>10.68977952158357</v>
+        <v>62.3870712900904</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>QC-SMOTE</t>
+          <t>OREM-M</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>0.8342586612174753</v>
+        <v>0.8372971000464409</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.7527882688424191</v>
+        <v>0.7757433716610412</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.9244299069239057</v>
+        <v>0.9236600338426921</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.7822365631956645</v>
+        <v>0.7731972949465373</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>50.78803411652556</v>
+        <v>10.68977952158357</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>SHSampler</t>
+          <t>QC-SMOTE</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>0.8220277651406549</v>
+        <v>0.8342586612174753</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.8269071558433813</v>
+        <v>0.7527882688424191</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.9254090245530501</v>
+        <v>0.9244299069239057</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.7690078573756405</v>
+        <v>0.7822365631956645</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.2300179405782432</v>
+        <v>50.78803411652556</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>SMOM</t>
+          <t>SHSampler</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>0.8369496447293582</v>
+        <v>0.8220277651406549</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.7746052659770132</v>
+        <v>0.8269071558433813</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.9248433778968425</v>
+        <v>0.9254090245530501</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.7782290877038535</v>
+        <v>0.7690078573756405</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>81.33422319431654</v>
+        <v>0.2300179405782432</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>SOUP</t>
+          <t>SMOM</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>0.8318354451750747</v>
+        <v>0.8369496447293582</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.7866171698919601</v>
+        <v>0.7746052659770132</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.9238422589085092</v>
+        <v>0.9248433778968425</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.7709596837793576</v>
+        <v>0.7782290877038535</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>98.59948736594167</v>
+        <v>81.33422319431654</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>SPE</t>
+          <t>SOUP</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>0.7752583120848933</v>
+        <v>0.8318354451750747</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.8550337978381498</v>
+        <v>0.7866171698919601</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.9175352510010499</v>
+        <v>0.9238422589085092</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.7608218060206903</v>
+        <v>0.7709596837793576</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>12.28088008824388</v>
+        <v>98.59948736594167</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>AdaBoostAD</t>
-        </is>
+          <t>SPE</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>0.7752583120848933</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>0.8550337978381498</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>0.9175352510010499</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>0.7608218060206903</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>12.28088008824388</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>DualLexiBoost</t>
+          <t>AdaBoostAD</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>LexiBoost</t>
+          <t>DualLexiBoost</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>MC-RBO</t>
+          <t>LexiBoost</t>
         </is>
       </c>
     </row>
@@ -941,7 +956,7 @@
         <v>1.75</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="D2" s="6" t="n">
         <v>1</v>
@@ -956,7 +971,7 @@
         <v>1</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -966,10 +981,10 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="D3" s="6" t="n">
         <v>4</v>
@@ -981,10 +996,10 @@
         <v>3</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -994,10 +1009,10 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>5</v>
@@ -1009,7 +1024,7 @@
         <v>5</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H4" s="6" t="n">
         <v>4</v>
@@ -1050,10 +1065,10 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>2</v>
@@ -1065,7 +1080,7 @@
         <v>11</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>5</v>
@@ -1078,10 +1093,10 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>7</v>
+        <v>7.25</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>3</v>
@@ -1093,7 +1108,7 @@
         <v>8</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H7" s="6" t="n">
         <v>8</v>
@@ -1106,13 +1121,13 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>3</v>
@@ -1121,7 +1136,7 @@
         <v>2</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>1</v>
@@ -1134,13 +1149,13 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>8.25</v>
+        <v>8.75</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>9.6</v>
+        <v>10.2</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>6</v>
@@ -1149,10 +1164,10 @@
         <v>7</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -1162,13 +1177,13 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>9.6</v>
+        <v>10.2</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>1</v>
@@ -1177,10 +1192,10 @@
         <v>6</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -1190,13 +1205,13 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>9</v>
+        <v>9.25</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>14</v>
@@ -1218,10 +1233,10 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>9</v>
+        <v>9.25</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D12" s="6" t="n">
         <v>8</v>
@@ -1233,177 +1248,198 @@
         <v>10</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>FRAME</t>
+          <t>MC-RBO</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
         <v>10</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>9.4</v>
+        <v>10.2</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>MC-CCR</t>
+          <t>FRAME</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
         <v>10.5</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D14" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E14" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="E14" s="6" t="n">
-        <v>15</v>
-      </c>
       <c r="F14" s="6" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>SPE</t>
+          <t>MC-CCR</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>12.25</v>
+        <v>11.5</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>11.6</v>
+        <v>9.6</v>
       </c>
       <c r="D15" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="E15" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="F15" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H15" s="6" t="n">
         <v>2</v>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="G15" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>DBCF</t>
+          <t>SPE</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>13.6</v>
+        <v>12.2</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>EB-SMOTE</t>
+          <t>DBCF</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>14</v>
+        <v>14.75</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>12.4</v>
+        <v>14.4</v>
       </c>
       <c r="D17" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="E17" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="F17" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G17" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="H17" s="6" t="n">
         <v>13</v>
-      </c>
-      <c r="G17" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>AdaBoostAD</t>
-        </is>
+          <t>EB-SMOTE</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>DualLexiBoost</t>
+          <t>AdaBoostAD</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>LexiBoost</t>
+          <t>DualLexiBoost</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>MC-RBO</t>
+          <t>LexiBoost</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1452,7 +1488,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>参与均值与排名的完整模型 16 个; 数据集覆盖不全未参与 5 个</t>
+          <t>参与均值与排名的完整模型 17 个; 数据集覆盖不全未参与 4 个</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1512,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>DualLexiBoost: 要求 153 个数据集, 有效结果 111 个, 缺失 42 个 (32 个 bearing, 4 个 heart, 4 个 software_defect, 2 个 keel); 不参与均值与排名, 仅保留模型名</t>
+          <t>DualLexiBoost: 要求 153 个数据集, 有效结果 113 个, 缺失 40 个 (32 个 bearing, 4 个 heart, 4 个 software_defect); 不参与均值与排名, 仅保留模型名</t>
         </is>
       </c>
     </row>
@@ -1500,55 +1536,55 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>MC-RBO: 要求 153 个数据集, 有效结果 152 个, 缺失 1 个 (1 个 bearing); 不参与均值与排名, 仅保留模型名</t>
+          <t>Ours: 要求 153 个数据集, 有效结果 113 个, 缺失 40 个 (32 个 bearing, 4 个 heart, 4 个 software_defect); 不参与均值与排名, 仅保留模型名</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>排除模型</t>
+          <t>失败单元</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Ours: 要求 153 个数据集, 有效结果 112 个, 缺失 41 个 (32 个 bearing, 4 个 heart, 4 个 software_defect, 1 个 keel); 不参与均值与排名, 仅保留模型名</t>
+          <t>MC-RBO × IR30_Ottawa: 指标为 NaN/Error, 视为未跑出结果, 不参与聚合</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>失败单元</t>
+          <t>名称规范化</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>DualLexiBoost × pima: 指标为 NaN/Error, 视为未跑出结果, 不参与聚合</t>
+          <t>模型名统一: glos(7 行) → GLOS</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>失败单元</t>
+          <t>名称规范化</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Ours × wisconsin: 指标为 NaN/Error, 视为未跑出结果, 不参与聚合</t>
+          <t>模型名统一: mc_ccr(7 行) → MC-CCR</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>失败单元</t>
+          <t>名称规范化</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>DualLexiBoost × yeast: 指标为 NaN/Error, 视为未跑出结果, 不参与聚合</t>
+          <t>模型名统一: mc_rbo(7 行) → MC-RBO</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1596,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>模型名统一: glos(7 行) → GLOS</t>
+          <t>模型名统一: mdo(7 行) → MDO</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1608,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>模型名统一: mc_ccr(7 行) → MC-CCR</t>
+          <t>模型名统一: nromm(7 行) → NROMM</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1620,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>模型名统一: mc_rbo(7 行) → MC-RBO</t>
+          <t>模型名统一: orem_m(7 行) → OREM-M</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1632,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>模型名统一: mdo(7 行) → MDO</t>
+          <t>模型名统一: shsampler(6 行) → SHSampler</t>
         </is>
       </c>
     </row>
@@ -1608,7 +1644,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>模型名统一: nromm(7 行) → NROMM</t>
+          <t>模型名统一: smom(6 行) → SMOM</t>
         </is>
       </c>
     </row>
@@ -1619,42 +1655,6 @@
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>模型名统一: orem_m(7 行) → OREM-M</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>名称规范化</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>模型名统一: shsampler(6 行) → SHSampler</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>名称规范化</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>模型名统一: smom(6 行) → SMOM</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>名称规范化</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>模型名统一: soup(6 行) → SOUP</t>
         </is>
